--- a/hints.xlsx
+++ b/hints.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Xenia160100\Documents\GitHub\aozakana\hint_test\hint_test\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Xenia160100\Documents\GitHub\aozakana\GOD-KNOWS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{6A0C1CC8-FABB-4399-8FA0-3BBF52C4F186}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFCD2EEE-B808-4B5F-9A8E-538C48C33850}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" xr2:uid="{E69F9E97-3D7F-4EEF-852A-49F659DA4124}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="146">
   <si>
     <t>Level1</t>
   </si>
@@ -551,24 +551,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>全体</t>
-    <rPh sb="0" eb="2">
-      <t>ゼンタイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ノイズが被さっていて、下に書かれた謎を推測することはできなさそうです。 このままではステップ4を解くことができません。 しかし、あなたは1つだけ答えを知ることができます。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>試しにオラクルが告げる「理論」と入力してみましょう。これがステップ4の答えです。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ステップ5のヒント</t>
-  </si>
-  <si>
     <t>全体構造</t>
     <rPh sb="0" eb="4">
       <t>ゼンタイコウゾウ</t>
@@ -580,10 +562,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>この画像には、四隅にあるかぎかっこに似た形の記号のうち、右上と右下のものがありません。 では、どのような状況が想定できるでしょうか。手がかりは1番最初に送られた画像にあります。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>1番最初に送られた画像では、2つの答えがある問題に対して、次に送信されるべき画像が半分ずつ送信されていました。 では、これを今の状況に照らし合わせて矛盾のないようにするにはどうすればよいでしょうか。</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -595,19 +573,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>どこから手を付ければよいか分からない</t>
-    <rPh sb="4" eb="5">
-      <t>テ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ツ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>ワ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>答え</t>
     <rPh sb="0" eb="1">
       <t>コタ</t>
@@ -615,258 +580,1363 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>立方体を1周させるルートは画像のようになります（辺上の壁の位置は確定しません）。&lt;br&gt;ルートが分かったら、立方体の配置に関するルールを分析しましょう。 ルールに注目して考えれば、立方体をどこに配置したか、1つに確定します。&lt;img src="img/4_matome_ans.png" class="w-full"&gt;</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>この謎は立方体を全てのマスを通るように転がして一周させるというものです。 ノイズに隠れてはいますが、この盤面で立方体を一周させる方法は（スタート地点の違いと出発する方向を無視すれば）1通りしかありません。 目に見えている壁の位置からその通り方を導きましょう。&lt;br&gt;なお、盤面は5×5の大きさで、中央のマスを除いて壁になっているマスは存在しません。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ステップ4の1つ目の答え「理論」から、ステップ4の問題を復元するためのヒントです。&lt;br&gt;すでにステップ4の問題を復元できていて、ステップ4のもう1つの答えを求めたい方は、「さらにその先のヒント」をご覧ください。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ステップ4には&lt;b&gt;答えが2つあります&lt;/b&gt;。これにより、ステップ5の謎画像が2つに分割されて送信されてしまっています。&lt;br&gt;また、それによりステップ2のまとめの謎の法則「答えの文字数で分割された謎は、その答えの文字数目を表す」が適用されてしまい、オラクルは本来2文字であるステップ5の答えの前半1文字だけを告げていることになります。&lt;br&gt;あなたがすべきことは、すでに分かっているステップ4の答えからステップ4のもう1つの答えを推測し、ステップ5の謎画像の残り半分を手に入れることです。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>立方体には、「ん」の面が上になる文字を読むという読み方と、進行方向3マス目で「ん」の面が上になるというルールがありました。 これらから、答えが「理論」になるためには、前のヒントにあるルートに沿って「り」のマスから3マス離れたマスに立方体を配置するということが分かります。&lt;br&gt;「り」のマスの先で立方体を転がすと「ろ」「ん」になると考えて進行方向を特定しましょう。 進行方向が分かれば、その方向に「り」から3マス戻った先が配置マスであり、同時にAの答えの1文字目でもあります。</t>
-  </si>
-  <si>
-    <t>Aの答えの1文字目は「も」、最後の文字は「ち」です。&lt;img src="img/4_matome_ans2.png" class="w-full"&gt;</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Aの問題の盤面の復元方法</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>まずは、ステップ4のまとめの謎の答えが「理論」になるよう、まとめの謎のルールを分析しましょう。 これによりAの答えの頭文字、最後の文字が分かります。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>まずは、Aの問題のノイズの下にある二重枠に注目しましょう。この二重枠に見覚えがないでしょうか。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Aの問題の二重枠は、ステップ1の5問目にありました。 ステップ1の5問目の答えは「ドン」です。 メダルを埋めること、答えが「ドン」になることから、ノイズの下を特定して二重枠の中身を復元しましょう。&lt;img src="img/1_5_noise.png" class="w-full"&gt;</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>二重枠は画像のようになっています。&lt;img src="img/1_5.png" class="w-full"&gt;</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Aの答え</t>
+    <t>▶と「ボード」という言葉はステップ2のまとめの謎にありました。 このボードの謎の切り取られ方を見ると、答えが「し」から始まる3文字であると分かります。 そのような答えになる謎を探し出し、「ボード」を復元しましょう。&lt;img src="img/1_matome_ans.png" class="w-full"&gt;</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「し」から始まる3文字の答えになる謎は1つしかありません。 それは、ステップ1のまとめの謎、「しぜん」です。&lt;br&gt;この謎がステップ1のまとめの謎であることに注意して、ステップ2で見えている箇所からボードを復元しましょう。&lt;br&gt;なお、ステップ1の謎の答えは「なつかぜ」「しんがた」「したしみ」「まぜんた」「どん」です。&lt;img src="img/1_6_noise.png" class="w-full"&gt;</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステップ1の答えを埋めると答えが「しぜん」になるようなボード盤面は、画像のように1通りに確定します。&lt;br&gt;&lt;br&gt;みど&lt;br&gt;しんがた&lt;br&gt;た　　ん&lt;br&gt;し　　ぜかつな&lt;br&gt;　　　ま&lt;img src="img/1_board.png" class="w-full"&gt;</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>解きやすい順番</t>
+    <rPh sb="0" eb="1">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ジュンバン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>この二重枠に見覚えがないでしょうか。前の問題を振り返ってみましょう。</t>
+    <rPh sb="2" eb="4">
+      <t>ニジュウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ワク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ミオボ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>マエ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>モンダイ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>カエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ヒント3</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メダルの色の「きん」「ぎん」「どう」が埋まったときに答えがドンになるには、もともと見えている範囲を考慮すると、画像のようになります。&lt;img src="img/1_5.png" class="w-full"&gt;&lt;br&gt;では、ここに埋めるべき漢字の音読みとは何でしょうか？パーツの個数が1、2、3個あること、「モク」という読みのものがあるという点から候補を絞りましょう。</t>
+    <rPh sb="4" eb="5">
+      <t>イロ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>ハンイ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>コウリョ</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>ガゾウ</t>
+    </rPh>
+    <rPh sb="114" eb="115">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="119" eb="121">
+      <t>カンジ</t>
+    </rPh>
+    <rPh sb="122" eb="124">
+      <t>オンヨ</t>
+    </rPh>
+    <rPh sb="127" eb="128">
+      <t>ナン</t>
+    </rPh>
+    <rPh sb="138" eb="140">
+      <t>コスウ</t>
+    </rPh>
+    <rPh sb="146" eb="147">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="159" eb="160">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="170" eb="171">
+      <t>テン</t>
+    </rPh>
+    <rPh sb="173" eb="175">
+      <t>コウホ</t>
+    </rPh>
+    <rPh sb="176" eb="177">
+      <t>シボ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>全体構造として、A、B、Cはそれぞれの問題を解くのに他の問題の答えが必要になります。解きやすい順番は提示しておきますが、ヒントは任意の順番で見ることができます。</t>
+    <rPh sb="0" eb="2">
+      <t>ゼンタイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウゾウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>モンダイ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ホカ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>モンダイ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>ジュンバン</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>テイジ</t>
+    </rPh>
+    <rPh sb="64" eb="66">
+      <t>ニンイ</t>
+    </rPh>
+    <rPh sb="67" eb="69">
+      <t>ジュンバン</t>
+    </rPh>
+    <rPh sb="70" eb="71">
+      <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C→A→B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ORACLEで答えが分かる問題はどれ？</t>
+    <rPh sb="7" eb="8">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>モンダイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>文字数に注目しましょう。3文字が答えになりうる問題はAとCだけです。</t>
+    <rPh sb="0" eb="3">
+      <t>モジスウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>チュウモク</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>モンダイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Aの問題の二重枠に注目しましょう。見覚えがないでしょうか。</t>
+    <rPh sb="2" eb="4">
+      <t>モンダイ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>ニジュウワク</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>チュウモク</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ミオボ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>この二重枠はステップ1の5問目にありました。ステップ1の5問目の答えが「ドン」になるためには、二重枠の下はどうなっていればよいでしょうか？</t>
+    <rPh sb="2" eb="4">
+      <t>ニジュウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ワク</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>モンメ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>モンメ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>ニジュウ</t>
+    </rPh>
+    <rPh sb="49" eb="50">
+      <t>ワク</t>
+    </rPh>
+    <rPh sb="51" eb="52">
+      <t>シタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>この二重枠はステップ1の5問目にありました。ステップ1の5問目の答えは「ドン」でした。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステップ1の5問目と同様に、Aの文字数も2文字であると推測できます。よって、消去法でORACLEはCに適用されると分かります。</t>
+    <rPh sb="7" eb="9">
+      <t>モンメ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ドウヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ORACLEはCに適用されるため、答えは理論であると分かります。</t>
+    <rPh sb="9" eb="11">
+      <t>テキヨウ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>リロン</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>木、林、森の音読みのモク、シン、リンを埋め、答えは「シン」になります。</t>
+    <rPh sb="0" eb="1">
+      <t>キ</t>
+    </rPh>
     <rPh sb="2" eb="3">
-      <t>コタ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>まとめの謎のルールの分析、およびAの問題の盤面の復元により特定できます。&lt;br&gt;まとめの謎のルールの分析のヒントは「どこから手を付ければよいか分からない」を、Aの問題の盤面の復元は「Aの問題の盤面の復元方法」のヒントをご覧ください。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>&lt;b&gt;もち（餅）&lt;/b&gt;&lt;br&gt;まとめの謎のルールの分析から、Aの答えの頭文字は「も」、最後の文字は「ち」であると分かります。&lt;br&gt;また、Aの問題の盤面の復元から、Aの答えが2文字であると分かります。&lt;br&gt;これらから、Aの答えは「もち」になります。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Cのボードの復元方法</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>まずはCの問題に描かれた▶と「ボード」という言葉に注目しましょう。これらに見覚えはないでしょうか。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>▶と「ボード」という言葉はステップ2のまとめの謎にありました。 このボードの謎の切り取られ方を見ると、答えが「し」から始まる3文字であると分かります。 そのような答えになる謎を探し出し、「ボード」を復元しましょう。&lt;img src="img/1_matome_ans.png" class="w-full"&gt;</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>「し」から始まる3文字の答えになる謎は1つしかありません。 それは、ステップ1のまとめの謎、「しぜん」です。&lt;br&gt;この謎がステップ1のまとめの謎であることに注意して、ステップ2で見えている箇所からボードを復元しましょう。&lt;br&gt;なお、ステップ1の謎の答えは「なつかぜ」「しんがた」「したしみ」「まぜんた」「どん」です。&lt;img src="img/1_6_noise.png" class="w-full"&gt;</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ステップ1の答えを埋めると答えが「しぜん」になるようなボード盤面は、画像のように1通りに確定します。&lt;br&gt;&lt;br&gt;みど&lt;br&gt;しんがた&lt;br&gt;た　　ん&lt;br&gt;し　　ぜかつな&lt;br&gt;　　　ま&lt;img src="img/1_board.png" class="w-full"&gt;</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Cの答えの最後の文字</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Cの答えの最後の文字は、Cのボードの復元と、Aの答えから特定できます。&lt;br&gt;Cのボードの復元のヒントは「Cのボードの復元方法」を、Aの答えは「Aの答え」をご覧ください。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>&lt;b&gt;ち&lt;/b&gt;&lt;br&gt;Cのボードの復元から、埋める言葉は2文字の言葉1つと4文字の言葉4つであると分かります。 よって、Aの答えが「もち」であることから、2文字の言葉である「もち」を埋める位置は1つに特定できます。&lt;br&gt;ボードの矢印は「もち」の2文字目のマスを最後に通るため、Cの答えの最後の文字は「ち」になります。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>立方体の「ん」の面の特定方法</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>まとめの謎の問題の分析から、立方体の青枠の面とその裏は「ん」でないことが分かります（実際に「も」のマスから「り」のマスまで3マス転がすことを考えてみてください）。&lt;br&gt;よって、立方体の「ん」の面は必ずBの答えに含まれます。&lt;br&gt;ここでは、Bの1文字目を除いた3文字のどこが「ん」なのか特定します。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Bの問題に注目しましょう。ここでは、2つのグループIとIIでしりとりし、それぞれの語群から文字を拾うようです。 ノイズの隙間から見える情報から、Bの答えは1、3文字目がグループIであり、2、4文字目がグループIIであることが分かります。&lt;br&gt;現在、Aの答えは特定できているので、グループIは全ての語が確定しますね。&lt;br&gt;Aの答えが分かっていない場合は「Aの答え」をご覧ください。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Aの答えは「もち」なので、グループIの語は&lt;br&gt;　もち→ちょうぼ→ぼりびあ→あかねこ→こうし&lt;br&gt;だと確定します。この中に「ん」を含む単語は存在しないため、Bの3文字目は「ん」でないと分かります。&lt;br&gt;では、グループIIのしりとりではどうなるでしょうか。そのためにはCの謎について考える必要があります。 もしCの答えの最後の文字が特定できていない場合は「Cの答えの最後の文字」をご覧ください。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Cの答えの最後の文字は「ち」でした。これにより、グループIIのしりとりは&lt;br&gt;　C（○○ち）→ちんか→かろりー→りょう→うかんむり&lt;br&gt;だと推測できます。では、この情報をもとにBの答えのうち確定する文字はないでしょうか。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ノイズの隙間には、Bの4文字目はグループIIの4番目の3文字であると書いてありました。その文字は「量」の「う」です。&lt;br&gt;よって、消去法によりBの2文字目が「ん」であると特定できます。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Cの答え</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Cの答えは、Cのボードの復元、Aの答え、立方体の「ん」の面の特定から特定できます。&lt;br&gt;Cのボードの復元のヒントは「Cのボードの復元方法」を、Aの答えは「Aの答え」を、立方体の「ん」の面は「立方体の『ん』の面の特定方法」をご覧ください。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ボードに埋める言葉のうち、現在分かっている情報は、&lt;br&gt;　①もち（A）&lt;br&gt;　②○ん○う（B）&lt;br&gt;　③りょぎん&lt;br&gt;　④にじいろ&lt;br&gt;　⑤○○○○&lt;br&gt;です。これらをボードに埋めるに当たり、まず2文字の「もち」が埋まります。&lt;br&gt;では、この「もち」と繋がる、2文字目が「ち」の4文字の言葉はどれでしょうか。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>①～⑤のうち、2文字目が「ち」になりうる4文字の言葉は⑤だけです。&lt;br&gt;　①もち（A）&lt;br&gt;　②○ん○う（B）&lt;br&gt;　③りょぎん&lt;br&gt;　④にじいろ&lt;br&gt;　⑤○ち○○&lt;br&gt;これにより、⑤が埋まる位置が特定できました。&lt;br&gt;続いて、縦向きの4文字のマスのうち、右側にあるマスに埋まる言葉を特定しましょう。2文字目が他の4文字の言葉の最後の文字になることに注目してください。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>2文字目が他の4文字の言葉の最後の文字になるような組み合わせは、②と③しかありません。&lt;br&gt;よって、縦向きの4文字のマスのうち右側にあるマスには、②○ん○う（B）が入ります。同時に、一番右側から左に伸びる4文字のマスには③りょぎんが入ります。&lt;br&gt;また、消去法により、縦向きの4文字のマスのうち左側にあるマスには、④にじいろが入ります。&lt;br&gt;これで、ボードに埋まる全ての言葉が特定できました。あとはCの答えを特定するだけです。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>&lt;b&gt;にんち（認知）&lt;/b&gt;&lt;br&gt;&lt;br&gt;　ろも&lt;br&gt;　いち？う&lt;br&gt;　じ　　？&lt;br&gt;　に　　んぎょり&lt;br&gt;　　　　？</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Cの問題の5つ目の単語の復元（一部）</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Cの5つ目の単語は、Cの答えを求める過程で1、2、4文字目が特定できます。 Cの答えの求め方は「Cの答え」をご覧ください。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>&lt;b&gt;いち？う&lt;/b&gt;</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Aの問題の全体像の復元</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Aの問題の全体像は、Aの盤面の復元とCの答え、Bの最後の文字から特定できます。&lt;br&gt;Aの盤面の復元のヒントは「Aの問題の盤面の復元方法」を、Cの答えは「Cの答え」を、Bの最後の文字は「立方体の『ん』の面の特定方法」をご覧ください。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Aの答えは「もち」、Cの答えは「にんち」、Bの答えの最後の文字は「う」ですので、これらをもとに今わかっている情報をまとめると次のようになります。&lt;br&gt;&lt;br&gt;　▼盤面　　　▼埋める文字&lt;br&gt;　１？？　　　？う（B）&lt;br&gt;　２？ち　　　にち（C）&lt;br&gt;　３も？　　　？？&lt;br&gt;注目するべきはCの答えである「にち」です。 問題文には「漢字のパーツの個数」とあるので、「にち」という漢字が複数のパーツでできていると考えたとき、どのようなパーツの組み合わせが考えられるでしょうか。&lt;br&gt;なお、音読みで埋めることに注意しましょう。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>「にち」は「日」であり、縦に「口」が2個組み合わさったと考えられます。&lt;br&gt;このとき、1個であれば「口（こう）」、3個であれば「目（もく）」になりますが、ここまでに特定した盤面・埋める文字と矛盾しません。&lt;br&gt;よって、Aの問題の盤面・埋める文字は次のようになります。&lt;br&gt;　▼盤面　　　▼埋める文字&lt;br&gt;　１こう　　　こう（B）&lt;br&gt;　２にち　　　にち（C）&lt;br&gt;　３もく　　　もく&lt;br&gt;では、この情報をもとに、Aの問題の全体像を復元してみましょう。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>&lt;img src="img/4_A.png" class="w-full"&gt;</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Bの問題の全体像の復元</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Bの問題の全体像を復元する必要はありません。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>さらにその先のヒント</t>
+      <t>ハヤシ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>モリ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>オンヨ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>コタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>純粋なしりとりです。AとCの答えが分かっていれば確定できます。まずはAとCを解きましょう。</t>
+    <rPh sb="0" eb="2">
+      <t>ジュンスイ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>カクテイ</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>ト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>答えは「シロアン（白あん）」です。</t>
+    <rPh sb="0" eb="1">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>シロ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>まずはBとCの答えを埋め、それを展開図とした立方体を作りましょう。以降のヒントはA~Cの答えを使用します。</t>
+    <rPh sb="7" eb="8">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>テンカイ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ズ</t>
+    </rPh>
+    <rPh sb="22" eb="25">
+      <t>リッポウタイ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>イコウ</t>
+    </rPh>
+    <rPh sb="44" eb="45">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>シヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>立方体の展開図は下のようになります。&lt;br&gt;　　り&lt;br&gt;　しろあん&lt;br&gt;　　ん&lt;br&gt;また、Aの答えの最初と最後の文字「し」「ん」を除いてSからGまでたどる方法は1通りしかありません。移動するルートが分かれば、配置方法・文字の拾い方も判明します。移動ルートを特定しましょう。&lt;br&gt;次のヒントでは移動ルートを提示します。</t>
+    <rPh sb="0" eb="3">
+      <t>リッポウタイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>テンカイ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ズ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>シタ</t>
+    </rPh>
+    <rPh sb="50" eb="51">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="53" eb="55">
+      <t>サイショ</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>サイゴ</t>
+    </rPh>
+    <rPh sb="59" eb="61">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="68" eb="69">
+      <t>ノゾ</t>
+    </rPh>
+    <rPh sb="80" eb="82">
+      <t>ホウホウ</t>
+    </rPh>
+    <rPh sb="84" eb="85">
+      <t>トオ</t>
+    </rPh>
+    <rPh sb="94" eb="96">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="102" eb="103">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="107" eb="109">
+      <t>ハイチ</t>
+    </rPh>
+    <rPh sb="109" eb="111">
+      <t>ホウホウ</t>
+    </rPh>
+    <rPh sb="112" eb="114">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="115" eb="116">
+      <t>ヒロ</t>
+    </rPh>
+    <rPh sb="117" eb="118">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="125" eb="127">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="131" eb="133">
+      <t>トクテイ</t>
+    </rPh>
+    <rPh sb="143" eb="144">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="150" eb="152">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="156" eb="158">
+      <t>テイジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>移動ルートは以下のようになります。このルートで1回転がすと水色の面が上になるように配置し、ア行の面が上になるマスの文字を読みましょう。&lt;img src="img/4_matome_ans.png" class="w-full"&gt;</t>
+    <rPh sb="0" eb="2">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>コロ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ミズイロ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>メン</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>ハイチ</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>ギョウ</t>
+    </rPh>
+    <rPh sb="48" eb="49">
+      <t>メン</t>
+    </rPh>
+    <rPh sb="50" eb="51">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="57" eb="59">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="60" eb="61">
+      <t>ヨ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>答えは「ぜったい（絶対）」です。</t>
+    <rPh sb="0" eb="1">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ゼッタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>この画像には、四隅にあるかぎかっこに似た形の記号のうち、右上と右下のものがありません。&lt;br&gt;では、どのような状況が想定できるでしょうか。手がかりは1番最初に送られた画像にあります。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B→C→A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>パーツは「口」です。</t>
     <rPh sb="5" eb="6">
+      <t>クチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「モク」は3個のパーツが組み合わさった漢字です。</t>
+    <rPh sb="6" eb="7">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ク</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>カンジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A、Cの答えが分かっていなくても、グループの残りの言葉だけである程度しりとりが成立します。ますはこれらの言葉でしりとりを行いましょう。</t>
+    <rPh sb="4" eb="5">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ノコ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>コトバ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>テイド</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>セイリツ</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>コトバ</t>
+    </rPh>
+    <rPh sb="60" eb="61">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>グループIのしりとりは「ちょうぼ、ぼりびあ、あかねこ、こうし」、グループIIは「ちんか、かろりー、りょう、うかんむり」です。これらにしりとりが成立するように1単語追加することを考えましょう。次のヒントで示されるある事実を用いれば、追加することができる位置をそれぞれ2箇所まで限定することができます。</t>
+    <rPh sb="71" eb="73">
+      <t>セイリツ</t>
+    </rPh>
+    <rPh sb="79" eb="81">
+      <t>タンゴ</t>
+    </rPh>
+    <rPh sb="81" eb="83">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="88" eb="89">
+      <t>カンガ</t>
+    </rPh>
+    <rPh sb="95" eb="96">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="101" eb="102">
+      <t>シメ</t>
+    </rPh>
+    <rPh sb="107" eb="109">
+      <t>ジジツ</t>
+    </rPh>
+    <rPh sb="110" eb="111">
+      <t>モチ</t>
+    </rPh>
+    <rPh sb="115" eb="117">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="125" eb="127">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="133" eb="135">
+      <t>カショ</t>
+    </rPh>
+    <rPh sb="137" eb="139">
+      <t>ゲンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>重要なのは、Cの問題にあるボードです。これを見ると、唯一の2文字であるAの答えの最後の文字を矢印の3文字目が通っています。これが意味するのは、AとCは最後の文字が同じであるということです。この事実を用いて、A、Cの答えを追加できる位置を絞りましょう。</t>
+    <rPh sb="96" eb="98">
+      <t>ジジツ</t>
+    </rPh>
+    <rPh sb="99" eb="100">
+      <t>モチ</t>
+    </rPh>
+    <rPh sb="107" eb="108">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="110" eb="112">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="115" eb="117">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="118" eb="119">
+      <t>シボ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ヒント5</t>
+  </si>
+  <si>
+    <t>A、Cの単語を追加できる位置は、「グループI、IIともに先頭」（A、Cいずれも「ち」で終わる答えの場合）または「グループI、IIの少なくとも1つは最後尾」（例えばAの答えが赤猫と講師の間にある「個々」だとすると、Cの答えの最後の文字も「こ」になりますが、最後の文字が「こ」の単語をグループIIに追加できる余地は最後尾しかない）のいずれかです。場合分けして考えましょう。</t>
+    <rPh sb="28" eb="30">
+      <t>セントウ</t>
+    </rPh>
+    <rPh sb="43" eb="44">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="65" eb="66">
+      <t>スク</t>
+    </rPh>
+    <rPh sb="73" eb="76">
+      <t>サイコウビ</t>
+    </rPh>
+    <rPh sb="127" eb="129">
+      <t>サイゴ</t>
+    </rPh>
+    <rPh sb="130" eb="132">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="137" eb="139">
+      <t>タンゴ</t>
+    </rPh>
+    <rPh sb="147" eb="149">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="152" eb="154">
+      <t>ヨチ</t>
+    </rPh>
+    <rPh sb="155" eb="158">
+      <t>サイコウビ</t>
+    </rPh>
+    <rPh sb="171" eb="173">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="173" eb="174">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="177" eb="178">
+      <t>カンガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステップ4の2つ目の答えを求めるためのヒントです。推奨する解きやすい順番は提示しておきますが、ヒントは任意の順番で見ることができます。&lt;br&gt;また、これらのヒントはCの「ボード」の中身を特定している前提で書かれています。もしまだボードを特定できていないのであれば、先に「ボードの正体」をご覧ください。</t>
+    <rPh sb="8" eb="9">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>モト</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>スイショウ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ジュンバン</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>テイジ</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>ニンイ</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>ジュンバン</t>
+    </rPh>
+    <rPh sb="57" eb="58">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="99" eb="101">
+      <t>ゼンテイ</t>
+    </rPh>
+    <rPh sb="102" eb="103">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="118" eb="120">
+      <t>トクテイ</t>
+    </rPh>
+    <rPh sb="132" eb="133">
       <t>サキ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>これは、すでにステップ4の問題を復元できていて、ステップ4のもう1つの答えを求めたい方のためのヒントです。&lt;br&gt;まだステップ4の問題を復元できていない方は、「その先のヒント」をご覧ください。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Aの問題の答え</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Aの問題の全体像を復元すると、画像のようになりました。&lt;br&gt;では、漢字のパーツが1個、2個、3個あり、音読みで「もく」となるものが含まれるものといえばなんでしょうか。 いずれも小学校で習う漢字です。&lt;img src="img/4_A.png" class="w-full"&gt;</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>&lt;b&gt;しん&lt;/b&gt;&lt;br&gt;&lt;br&gt;▼盤面　　　　　　　▼埋める文字&lt;br&gt;　１もく（木）　　　B（りん　または　しん）&lt;br&gt;　２りん（林）　　　C（りん　または　しん）&lt;br&gt;　３しん（森）　　　もく</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Cの問題の答え</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Cの答えは、Aの答えから特定することができます。&lt;br&gt;まだAの答えが分からない場合は、「Aの問題の答え」のヒントをご覧ください。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Cの埋める文字は「しん（A）」「○○○○（B）」「りょぎん」「にじいろ」「いち○う」であることが分かっています。&lt;br&gt;また、Aの答えを求める過程で、Cの答えの1文字目が「し」または「り」であることが分かっています。&lt;br&gt;では、矢印が最初に通る文字として可能性があるものは「し」と「り」のどちらでしょうか。&lt;img src="img/1_board.png" class="w-full"&gt;</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>矢印が最初に通る文字として可能性があるのは「りょぎん」の「り」のみです。 よって、1番左の縦4文字のマスには「りょぎん」が埋まります。同時に、Cの答えの1文字目は「し」になります。&lt;br&gt;&lt;br&gt;　んし&lt;br&gt;　ぎん？？&lt;br&gt;　ょ　　？&lt;br&gt;　り　　？？？？&lt;br&gt;　　　　？&lt;br&gt;しかし、これでは「ぎん？？」という言葉が必要になりますが、Cに埋める文字の中に「ぎん」で始まる4文字の言葉は存在しません。&lt;br&gt;では、どのような状況であればこの矛盾を解消できるでしょうか。手がかりは、語群が漢字で書かれていることにあります。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>もし「いち？う」という言葉が「いちょう（銀杏）」であれば、「ぎんなん」とも読むことができます。&lt;br&gt;すると、埋め方は次のように定まります。&lt;br&gt;&lt;br&gt;　んし&lt;br&gt;　ぎんなん&lt;br&gt;　ょ　　？&lt;br&gt;　り　　ろいじに&lt;br&gt;　　　　し&lt;br&gt;よって、Cの答えは「りろん」です。これはオラクルが告げている「理論」という状況とも一致します。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Bの問題の答え（一部）</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Bの答えのうち1、2、4文字目は、Cの答えを求める過程で特定することができます。&lt;br&gt;Cの答えを求める方法は「Cの問題の答え」をご覧ください。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>しろ？ん</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>まとめの謎の答え</t>
-    <rPh sb="4" eb="5">
+    <rPh sb="139" eb="141">
+      <t>ショウタイ</t>
+    </rPh>
+    <rPh sb="144" eb="145">
+      <t>ラン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボードの正体</t>
+    <rPh sb="4" eb="6">
+      <t>ショウタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Cに書かれている「ボード」の中身を特定するためのヒントです。</t>
+    <rPh sb="2" eb="3">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ナカミ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>トクテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>まずは描かれている▶と「ボード」という言葉に注目しましょう。これらに見覚えはないでしょうか。</t>
+    <rPh sb="3" eb="4">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>以下の考察により、A、Cの単語を追加する位置はグループI、IIともに先頭で、A、Cいずれも「ち」で終わる答えであることが分かります。これによりBの答えが確定します。&lt;br&gt;&lt;br&gt;「Cの答えがグループIIの最後尾につく」場合、Cの答えの1文字目は「り」です。また、このときBの答えの2文字目は「ろ」になります。まとめの謎の展開図からB、Cの答えの2文字目は一致するため、この場合Cの答えは「りろ？」となります。このような単語は「りろん」しかないので、どうやら1回目と同じ答えに帰着してしまいそうです。&lt;br&gt;一方、「Aの答えがグループIの最後尾につく」場合、Cの答えがグループIIの最後以外の場所に入ることを仮定すると、「しち」「しか」「しり」「しう」の4つだけです。これらのうちまとめの謎の盤面に2文字とも書かれているのは「しち」「しか」だけであり、また「しち」だとグループIがループしてしまうことから、この場合のAの答えは「しか」、Cの答えは「か？か」だと確定します。しかし、Cの問題のボードに注目するとCの答えが「か？か」になるためには埋める語群に「か」を含む4文字の単語が2つ以上なければならないはずですが、そうではなく矛盾します。よって、「Aの答えがグループIの最後尾につく」わけではないようです。</t>
+    <rPh sb="0" eb="2">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>コウサツ</t>
+    </rPh>
+    <rPh sb="60" eb="61">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="73" eb="74">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="76" eb="78">
+      <t>カクテイ</t>
+    </rPh>
+    <rPh sb="93" eb="94">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="110" eb="112">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="115" eb="116">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="119" eb="121">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="121" eb="122">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="138" eb="139">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="142" eb="144">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="144" eb="145">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="159" eb="160">
       <t>ナゾ</t>
     </rPh>
+    <rPh sb="161" eb="163">
+      <t>テンカイ</t>
+    </rPh>
+    <rPh sb="163" eb="164">
+      <t>ズ</t>
+    </rPh>
+    <rPh sb="170" eb="171">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="174" eb="176">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="176" eb="177">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="178" eb="180">
+      <t>イッチ</t>
+    </rPh>
+    <rPh sb="187" eb="189">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="191" eb="192">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="210" eb="212">
+      <t>タンゴ</t>
+    </rPh>
+    <rPh sb="230" eb="232">
+      <t>カイメ</t>
+    </rPh>
+    <rPh sb="233" eb="234">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="235" eb="236">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="238" eb="240">
+      <t>キチャク</t>
+    </rPh>
+    <rPh sb="254" eb="256">
+      <t>イッポウ</t>
+    </rPh>
+    <rPh sb="260" eb="261">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="269" eb="272">
+      <t>サイコウビ</t>
+    </rPh>
+    <rPh sb="276" eb="278">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="281" eb="282">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="291" eb="293">
+      <t>サイゴ</t>
+    </rPh>
+    <rPh sb="293" eb="295">
+      <t>イガイ</t>
+    </rPh>
+    <rPh sb="296" eb="298">
+      <t>バショ</t>
+    </rPh>
+    <rPh sb="299" eb="300">
+      <t>ハイ</t>
+    </rPh>
+    <rPh sb="304" eb="306">
+      <t>カテイ</t>
+    </rPh>
+    <rPh sb="344" eb="345">
+      <t>ナゾ</t>
+    </rPh>
+    <rPh sb="346" eb="348">
+      <t>バンメン</t>
+    </rPh>
+    <rPh sb="350" eb="352">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="354" eb="355">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="405" eb="407">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="410" eb="411">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="420" eb="421">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="430" eb="432">
+      <t>カクテイ</t>
+    </rPh>
+    <rPh sb="442" eb="444">
+      <t>モンダイ</t>
+    </rPh>
+    <rPh sb="449" eb="451">
+      <t>チュウモク</t>
+    </rPh>
+    <rPh sb="456" eb="457">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="471" eb="472">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="474" eb="476">
+      <t>ゴグン</t>
+    </rPh>
+    <rPh sb="481" eb="482">
+      <t>フク</t>
+    </rPh>
+    <rPh sb="484" eb="486">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="487" eb="489">
+      <t>タンゴ</t>
+    </rPh>
+    <rPh sb="492" eb="494">
+      <t>イジョウ</t>
+    </rPh>
+    <rPh sb="514" eb="516">
+      <t>ムジュン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>答えは「こんぼう（棍棒）」です。</t>
+    <rPh sb="0" eb="1">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>コンボウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>この問題を解くのはBの答えを求めてからでないと難しそうです。以降のヒントではBの答えを使用します。</t>
+    <rPh sb="2" eb="4">
+      <t>モンダイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>モト</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ムズカ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>イコウ</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>シヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Aの答えは唯一2文字ですので、埋まる場所が確定しそうです。まずは残りの箇所の埋め方を考えましょう。</t>
+    <rPh sb="2" eb="3">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ユイイツ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>バショ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>カクテイ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>ノコ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>カショ</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>カンガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「りょぎん」「にじいろ」「こんぼう（B)」は読み方が確定しますが、「銀杏」には2通りの読み方があります。もし一方で埋められなかった場合は、もう一方を試してみましょう。</t>
+    <rPh sb="22" eb="23">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>カクテイ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ギンナン</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>トオ</t>
+    </rPh>
+    <rPh sb="43" eb="44">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="45" eb="46">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>イッポウ</t>
+    </rPh>
+    <rPh sb="57" eb="58">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="65" eb="67">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="71" eb="73">
+      <t>イッポウ</t>
+    </rPh>
+    <rPh sb="74" eb="75">
+      <t>タメ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>答えは「にんち」です。また、同時にAの答えが「？ち」であることが確定します。&lt;br&gt;&lt;br&gt;　ろ？&lt;br&gt;　いちょう&lt;br&gt;　じ　　ぼ&lt;br&gt;　に　　んぎょり&lt;br&gt;　　　　こ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Aに埋まる言葉の要件を整理すると、「漢字の音読みが埋まる」「その漢字を構成するパーツの個数が1個、2個、3個の3種類」「そのうちの1つの音読みがモク」です。パーツの配置は「木」「林」「森」とは異なり、縦に積み重なります。</t>
+    <rPh sb="2" eb="3">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>コトバ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ヨウケン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>セイリ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>カンジ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>オンヨ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>カンジ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>コウセイ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>コスウ</t>
+    </rPh>
+    <rPh sb="47" eb="48">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="50" eb="51">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="53" eb="54">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>シュルイ</t>
+    </rPh>
+    <rPh sb="68" eb="70">
+      <t>オンヨ</t>
+    </rPh>
+    <rPh sb="82" eb="84">
+      <t>ハイチ</t>
+    </rPh>
+    <rPh sb="86" eb="87">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="89" eb="90">
+      <t>ハヤシ</t>
+    </rPh>
+    <rPh sb="92" eb="93">
+      <t>モリ</t>
+    </rPh>
+    <rPh sb="96" eb="97">
+      <t>コト</t>
+    </rPh>
+    <rPh sb="100" eb="101">
+      <t>タテ</t>
+    </rPh>
+    <rPh sb="102" eb="103">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="104" eb="105">
+      <t>カサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>立方体の展開図は下のようになります。&lt;br&gt;　　に&lt;br&gt;　こんぼう&lt;br&gt;　　ち&lt;br&gt;また、Aの答えの最初と最後の文字「も」「ち」を除いてSからGまでたどる方法は1通りしかありません。移動するルートが分かれば、配置方法・文字の拾い方も判明します。移動ルートを特定しましょう。&lt;br&gt;次のヒントでは移動ルートを提示します。</t>
+    <rPh sb="0" eb="3">
+      <t>リッポウタイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>テンカイ</t>
+    </rPh>
     <rPh sb="6" eb="7">
-      <t>コタ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>まとめの謎の答えは、Aの答え、Cの答え、Bの答えのうち特定できる文字から求めることができます。&lt;br&gt;Aの答え、Cの答え、Bの答えの一部の特定方法はそれぞれ「Aの問題の答え」「Cの問題の答え」「Bの問題の答え（一部）」をご覧ください。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>A、B、Cの答えはそれぞれ「しん」、「しろ？ん」、「りろん」でした。&lt;br&gt;まとめの謎のルールに従って、「し」のマスに立方体を配置しましょう。 また、今回は「ん」の面が2つあります。どちらの「ん」の面であっても、「ん」が上に来たタイミングでマスに書いてある文字を読んでみましょう。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>&lt;b&gt;あまのがわ（天の川）&lt;/b&gt;&lt;br&gt;立方体を「し」のマスに配置して転がしていくと、「こた？？あまのか（が）わ」と読むことができます。&lt;br&gt;前半が「答えは～」と書いてあると推測すれば、単語になる「あまのがわ」が答えだと推測できます。</t>
+      <t>ズ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>シタ</t>
+    </rPh>
+    <rPh sb="50" eb="51">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="53" eb="55">
+      <t>サイショ</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>サイゴ</t>
+    </rPh>
+    <rPh sb="59" eb="61">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="68" eb="69">
+      <t>ノゾ</t>
+    </rPh>
+    <rPh sb="80" eb="82">
+      <t>ホウホウ</t>
+    </rPh>
+    <rPh sb="84" eb="85">
+      <t>トオ</t>
+    </rPh>
+    <rPh sb="94" eb="96">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="102" eb="103">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="107" eb="109">
+      <t>ハイチ</t>
+    </rPh>
+    <rPh sb="109" eb="111">
+      <t>ホウホウ</t>
+    </rPh>
+    <rPh sb="112" eb="114">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="115" eb="116">
+      <t>ヒロ</t>
+    </rPh>
+    <rPh sb="117" eb="118">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="125" eb="127">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="131" eb="133">
+      <t>トクテイ</t>
+    </rPh>
+    <rPh sb="143" eb="144">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="150" eb="152">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="156" eb="158">
+      <t>テイジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>答えは「もち（餅）」です。マスには「口（コウ）」「日（ニチ）」「目（モク）」が埋まります。</t>
+    <rPh sb="0" eb="1">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>モチ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>クチ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ニチ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>ウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>移動ルートは以下のようになります。このルートで1回転がすと水色の面が上になるように配置し、ア行の面が上になるマスの文字を読みましょう。&lt;img src="img/4_matome_ans2.png" class="w-full"&gt;</t>
+    <rPh sb="0" eb="2">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>コロ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ミズイロ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>メン</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>ハイチ</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>ギョウ</t>
+    </rPh>
+    <rPh sb="48" eb="49">
+      <t>メン</t>
+    </rPh>
+    <rPh sb="50" eb="51">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="57" eb="59">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="60" eb="61">
+      <t>ヨ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最後のヒント</t>
+    <rPh sb="0" eb="2">
+      <t>サイゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ヒント</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>答えは「ことだま（言霊）」です。&lt;br&gt;なお、本来の謎では、数字が「らすとすてっぷのこたえはよんもじ」という文章の何文字目を拾うかを表しているという法則です。</t>
+    <rPh sb="9" eb="11">
+      <t>コトダマ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ホンライ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ナゾ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>スウジ</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>ブンショウ</t>
+    </rPh>
+    <rPh sb="57" eb="61">
+      <t>ナンモジメ</t>
+    </rPh>
+    <rPh sb="62" eb="63">
+      <t>ヒロ</t>
+    </rPh>
+    <rPh sb="66" eb="67">
+      <t>アラワ</t>
+    </rPh>
+    <rPh sb="74" eb="76">
+      <t>ホウソク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ラストステップのヒント</t>
+  </si>
+  <si>
+    <t>ステップ4には&lt;b&gt;答えが2つあります&lt;/b&gt;。これにより、ラストステップの謎画像が2つに分割されて送信されてしまっています。&lt;br&gt;また、それによりステップ2のまとめの謎の法則「答えの文字数で分割された謎は、その答えの文字数目を表す」が適用されてしまい、オラクルは本来4文字であるラストステップの答えの前半2文字だけを告げていることになります。&lt;br&gt;あなたがすべきことは、ステップ4のもう1つの答えを導き出し、ラストステップの謎画像の残り半分を手に入れることです。</t>
+    <rPh sb="202" eb="203">
+      <t>ミチビ</t>
+    </rPh>
+    <rPh sb="204" eb="205">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>答えは「ひとみ（瞳）」です。この答えを送信しましょう。ラストステップの謎のもう半分が手に入ります。</t>
+    <rPh sb="0" eb="1">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ヒトミ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ソウシン</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>ナゾ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>ハンブン</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>テ</t>
+    </rPh>
+    <rPh sb="44" eb="45">
+      <t>ハイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステップ4の2つの答えを送信し、ラストステップの謎全体が手に入った後のヒントです。</t>
+    <rPh sb="9" eb="10">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ソウシン</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ナゾ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ゼンタイ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>テ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ハイ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>アト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ORACLEが左右の答えを分割して告げている（ステップ2まとめ謎の法則）ため、2つを繋げて読みましょう。それがラストステップの答えです。</t>
+    <rPh sb="7" eb="9">
+      <t>サユウ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ブンカツ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>ナゾ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ホウソク</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>ツナ</t>
+    </rPh>
+    <rPh sb="45" eb="46">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="63" eb="64">
+      <t>コタ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1274,7 +2344,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC2235BC-2B2E-4F96-8645-BEB8D0B89BE3}">
-  <dimension ref="A1:E106"/>
+  <dimension ref="A1:E135"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -2003,14 +3073,8 @@
       <c r="A50" t="s">
         <v>86</v>
       </c>
-      <c r="B50" t="s">
-        <v>87</v>
-      </c>
-      <c r="C50" t="s">
-        <v>11</v>
-      </c>
       <c r="E50" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -2018,835 +3082,790 @@
         <v>86</v>
       </c>
       <c r="B51" t="s">
-        <v>87</v>
-      </c>
-      <c r="C51" t="s">
-        <v>8</v>
+        <v>95</v>
       </c>
       <c r="E51" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B52" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="C52" t="s">
         <v>11</v>
       </c>
       <c r="E52" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B53" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="C53" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E53" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B54" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="C54" t="s">
         <v>63</v>
       </c>
       <c r="E54" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B55" t="s">
+        <v>101</v>
+      </c>
+      <c r="C55" t="s">
         <v>91</v>
       </c>
-      <c r="C55" t="s">
-        <v>8</v>
-      </c>
       <c r="E55" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A56" s="2" t="s">
-        <v>90</v>
+      <c r="A56" t="s">
+        <v>86</v>
       </c>
       <c r="B56" t="s">
-        <v>95</v>
-      </c>
-      <c r="C56" s="2"/>
+        <v>29</v>
+      </c>
+      <c r="C56" t="s">
+        <v>11</v>
+      </c>
       <c r="E56" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B57" t="s">
-        <v>95</v>
+        <v>29</v>
       </c>
       <c r="C57" t="s">
-        <v>96</v>
-      </c>
-      <c r="D57" t="s">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="E57" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B58" t="s">
-        <v>95</v>
+        <v>29</v>
       </c>
       <c r="C58" t="s">
-        <v>96</v>
-      </c>
-      <c r="D58" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="E58" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B59" t="s">
-        <v>95</v>
+        <v>29</v>
       </c>
       <c r="C59" t="s">
-        <v>96</v>
-      </c>
-      <c r="D59" t="s">
-        <v>63</v>
+        <v>91</v>
       </c>
       <c r="E59" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B60" t="s">
-        <v>95</v>
+        <v>33</v>
       </c>
       <c r="C60" t="s">
-        <v>96</v>
-      </c>
-      <c r="D60" t="s">
-        <v>64</v>
+        <v>11</v>
       </c>
       <c r="E60" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B61" t="s">
-        <v>95</v>
+        <v>33</v>
       </c>
       <c r="C61" t="s">
-        <v>96</v>
-      </c>
-      <c r="D61" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E61" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B62" t="s">
-        <v>95</v>
-      </c>
-      <c r="C62" t="s">
-        <v>104</v>
-      </c>
-      <c r="D62" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="E62" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B63" t="s">
-        <v>95</v>
+        <v>23</v>
       </c>
       <c r="C63" t="s">
-        <v>104</v>
-      </c>
-      <c r="D63" t="s">
-        <v>61</v>
-      </c>
-      <c r="E63" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>11</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B64" t="s">
-        <v>95</v>
+        <v>23</v>
       </c>
       <c r="C64" t="s">
-        <v>104</v>
-      </c>
-      <c r="D64" t="s">
+        <v>62</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="A65" t="s">
+        <v>86</v>
+      </c>
+      <c r="B65" t="s">
+        <v>23</v>
+      </c>
+      <c r="C65" t="s">
         <v>97</v>
       </c>
-      <c r="E64" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A65" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B65" t="s">
-        <v>95</v>
-      </c>
-      <c r="C65" t="s">
-        <v>109</v>
-      </c>
-      <c r="E65" t="s">
-        <v>110</v>
+      <c r="E65" s="1" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B66" t="s">
-        <v>95</v>
+        <v>23</v>
       </c>
       <c r="C66" t="s">
-        <v>109</v>
-      </c>
-      <c r="D66" t="s">
-        <v>97</v>
-      </c>
-      <c r="E66" t="s">
-        <v>111</v>
+        <v>91</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" t="s">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="B67" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="C67" t="s">
-        <v>112</v>
-      </c>
-      <c r="D67" t="s">
         <v>11</v>
       </c>
       <c r="E67" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" t="s">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="B68" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="C68" t="s">
-        <v>112</v>
-      </c>
-      <c r="D68" t="s">
         <v>61</v>
       </c>
       <c r="E68" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" t="s">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="B69" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="C69" t="s">
-        <v>112</v>
-      </c>
-      <c r="D69" t="s">
         <v>63</v>
       </c>
       <c r="E69" t="s">
-        <v>115</v>
+        <v>89</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" t="s">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="B70" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="C70" t="s">
-        <v>112</v>
-      </c>
-      <c r="D70" t="s">
-        <v>97</v>
+        <v>8</v>
       </c>
       <c r="E70" t="s">
-        <v>116</v>
+        <v>142</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B71" t="s">
         <v>90</v>
       </c>
-      <c r="B71" t="s">
+      <c r="C71" s="2"/>
+      <c r="E71" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A72" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B72" t="s">
+        <v>90</v>
+      </c>
+      <c r="C72" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C71" t="s">
-        <v>117</v>
-      </c>
-      <c r="E71" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A72" t="s">
-        <v>90</v>
-      </c>
-      <c r="B72" t="s">
-        <v>95</v>
-      </c>
-      <c r="C72" t="s">
-        <v>117</v>
-      </c>
-      <c r="D72" t="s">
-        <v>97</v>
-      </c>
       <c r="E72" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B73" t="s">
         <v>90</v>
       </c>
-      <c r="B73" t="s">
-        <v>95</v>
-      </c>
-      <c r="C73" t="s">
-        <v>120</v>
+      <c r="C73" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="E73" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A74" t="s">
+      <c r="A74" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B74" t="s">
         <v>90</v>
       </c>
-      <c r="B74" t="s">
-        <v>95</v>
-      </c>
-      <c r="C74" t="s">
-        <v>120</v>
+      <c r="C74" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="D74" t="s">
         <v>11</v>
       </c>
       <c r="E74" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A75" t="s">
+      <c r="A75" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B75" t="s">
         <v>90</v>
       </c>
-      <c r="B75" t="s">
-        <v>95</v>
-      </c>
-      <c r="C75" t="s">
-        <v>120</v>
+      <c r="C75" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="D75" t="s">
         <v>61</v>
       </c>
       <c r="E75" t="s">
-        <v>123</v>
+        <v>92</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A76" t="s">
+      <c r="A76" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B76" t="s">
         <v>90</v>
       </c>
-      <c r="B76" t="s">
-        <v>95</v>
-      </c>
-      <c r="C76" t="s">
-        <v>120</v>
+      <c r="C76" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="D76" t="s">
         <v>63</v>
       </c>
       <c r="E76" t="s">
-        <v>124</v>
+        <v>93</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A77" t="s">
+      <c r="A77" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B77" t="s">
         <v>90</v>
       </c>
-      <c r="B77" t="s">
-        <v>95</v>
-      </c>
-      <c r="C77" t="s">
-        <v>120</v>
+      <c r="C77" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="D77" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E77" t="s">
-        <v>125</v>
+        <v>94</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A78" s="2" t="s">
+      <c r="A78" t="s">
+        <v>141</v>
+      </c>
+      <c r="B78" t="s">
         <v>90</v>
       </c>
-      <c r="B78" t="s">
-        <v>95</v>
-      </c>
       <c r="C78" t="s">
-        <v>126</v>
+        <v>29</v>
+      </c>
+      <c r="D78" t="s">
+        <v>11</v>
       </c>
       <c r="E78" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" t="s">
+        <v>141</v>
+      </c>
+      <c r="B79" t="s">
         <v>90</v>
       </c>
-      <c r="B79" t="s">
-        <v>95</v>
-      </c>
       <c r="C79" t="s">
-        <v>126</v>
+        <v>29</v>
       </c>
       <c r="D79" t="s">
-        <v>11</v>
+        <v>61</v>
       </c>
       <c r="E79" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" t="s">
+        <v>141</v>
+      </c>
+      <c r="B80" t="s">
         <v>90</v>
       </c>
-      <c r="B80" t="s">
-        <v>95</v>
-      </c>
       <c r="C80" t="s">
-        <v>126</v>
+        <v>29</v>
       </c>
       <c r="D80" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E80" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" t="s">
+        <v>141</v>
+      </c>
+      <c r="B81" t="s">
         <v>90</v>
       </c>
-      <c r="B81" t="s">
-        <v>95</v>
-      </c>
       <c r="C81" t="s">
-        <v>126</v>
+        <v>29</v>
       </c>
       <c r="D81" t="s">
-        <v>63</v>
+        <v>91</v>
       </c>
       <c r="E81" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" t="s">
+        <v>141</v>
+      </c>
+      <c r="B82" t="s">
         <v>90</v>
       </c>
-      <c r="B82" t="s">
-        <v>95</v>
-      </c>
       <c r="C82" t="s">
-        <v>126</v>
+        <v>33</v>
       </c>
       <c r="D82" t="s">
-        <v>97</v>
+        <v>11</v>
       </c>
       <c r="E82" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A83" s="2" t="s">
+      <c r="A83" t="s">
+        <v>141</v>
+      </c>
+      <c r="B83" t="s">
         <v>90</v>
       </c>
-      <c r="B83" t="s">
-        <v>95</v>
-      </c>
       <c r="C83" t="s">
-        <v>132</v>
+        <v>33</v>
+      </c>
+      <c r="D83" t="s">
+        <v>62</v>
       </c>
       <c r="E83" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" t="s">
+        <v>141</v>
+      </c>
+      <c r="B84" t="s">
         <v>90</v>
       </c>
-      <c r="B84" t="s">
-        <v>95</v>
-      </c>
       <c r="C84" t="s">
-        <v>132</v>
+        <v>33</v>
       </c>
       <c r="D84" t="s">
         <v>97</v>
       </c>
       <c r="E84" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A85" s="2" t="s">
+      <c r="A85" t="s">
+        <v>141</v>
+      </c>
+      <c r="B85" t="s">
         <v>90</v>
       </c>
-      <c r="B85" t="s">
-        <v>95</v>
-      </c>
       <c r="C85" t="s">
-        <v>135</v>
+        <v>33</v>
+      </c>
+      <c r="D85" t="s">
+        <v>64</v>
       </c>
       <c r="E85" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" ht="234" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" t="s">
+        <v>141</v>
+      </c>
+      <c r="B86" t="s">
         <v>90</v>
       </c>
-      <c r="B86" t="s">
-        <v>95</v>
-      </c>
       <c r="C86" t="s">
-        <v>135</v>
+        <v>33</v>
       </c>
       <c r="D86" t="s">
-        <v>11</v>
-      </c>
-      <c r="E86" t="s">
-        <v>137</v>
+        <v>122</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" t="s">
+        <v>141</v>
+      </c>
+      <c r="B87" t="s">
         <v>90</v>
       </c>
-      <c r="B87" t="s">
-        <v>95</v>
-      </c>
       <c r="C87" t="s">
-        <v>135</v>
+        <v>33</v>
       </c>
       <c r="D87" t="s">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="E87" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" t="s">
+        <v>141</v>
+      </c>
+      <c r="B88" t="s">
         <v>90</v>
       </c>
-      <c r="B88" t="s">
-        <v>95</v>
-      </c>
       <c r="C88" t="s">
-        <v>135</v>
-      </c>
-      <c r="D88" t="s">
-        <v>97</v>
+        <v>34</v>
       </c>
       <c r="E88" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" t="s">
+        <v>141</v>
+      </c>
+      <c r="B89" t="s">
         <v>90</v>
       </c>
-      <c r="B89" t="s">
-        <v>95</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>140</v>
+      <c r="C89" t="s">
+        <v>34</v>
+      </c>
+      <c r="D89" t="s">
+        <v>11</v>
       </c>
       <c r="E89" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A90" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A90" s="2" t="s">
+      <c r="B90" t="s">
         <v>90</v>
       </c>
-      <c r="B90" t="s">
-        <v>142</v>
-      </c>
-      <c r="C90" s="4"/>
+      <c r="C90" t="s">
+        <v>34</v>
+      </c>
+      <c r="D90" t="s">
+        <v>61</v>
+      </c>
       <c r="E90" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" t="s">
+        <v>141</v>
+      </c>
+      <c r="B91" t="s">
         <v>90</v>
       </c>
-      <c r="B91" t="s">
-        <v>142</v>
-      </c>
       <c r="C91" t="s">
-        <v>144</v>
+        <v>34</v>
       </c>
       <c r="D91" t="s">
-        <v>11</v>
+        <v>91</v>
       </c>
       <c r="E91" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" t="s">
+        <v>141</v>
+      </c>
+      <c r="B92" t="s">
         <v>90</v>
       </c>
-      <c r="B92" t="s">
-        <v>142</v>
-      </c>
       <c r="C92" t="s">
-        <v>144</v>
+        <v>23</v>
       </c>
       <c r="D92" t="s">
-        <v>97</v>
-      </c>
-      <c r="E92" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A93" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" ht="72" x14ac:dyDescent="0.55000000000000004">
+      <c r="A93" t="s">
+        <v>141</v>
+      </c>
+      <c r="B93" t="s">
         <v>90</v>
       </c>
-      <c r="B93" t="s">
-        <v>142</v>
-      </c>
       <c r="C93" t="s">
-        <v>147</v>
-      </c>
-      <c r="E93" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>23</v>
+      </c>
+      <c r="D93" t="s">
+        <v>61</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" ht="54" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" t="s">
+        <v>141</v>
+      </c>
+      <c r="B94" t="s">
         <v>90</v>
       </c>
-      <c r="B94" t="s">
-        <v>142</v>
-      </c>
       <c r="C94" t="s">
-        <v>147</v>
+        <v>23</v>
       </c>
       <c r="D94" t="s">
-        <v>11</v>
-      </c>
-      <c r="E94" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>63</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" t="s">
+        <v>141</v>
+      </c>
+      <c r="B95" t="s">
         <v>90</v>
       </c>
-      <c r="B95" t="s">
-        <v>142</v>
-      </c>
       <c r="C95" t="s">
-        <v>147</v>
+        <v>23</v>
       </c>
       <c r="D95" t="s">
-        <v>61</v>
-      </c>
-      <c r="E95" t="s">
-        <v>150</v>
+        <v>91</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" t="s">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="B96" t="s">
-        <v>142</v>
-      </c>
-      <c r="C96" t="s">
-        <v>147</v>
-      </c>
-      <c r="D96" t="s">
-        <v>97</v>
-      </c>
-      <c r="E96" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A97" s="2" t="s">
-        <v>90</v>
+        <v>138</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A97" t="s">
+        <v>141</v>
       </c>
       <c r="B97" t="s">
-        <v>142</v>
-      </c>
-      <c r="C97" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="E97" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>138</v>
+      </c>
+      <c r="C97" t="s">
+        <v>139</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" t="s">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="B98" t="s">
-        <v>142</v>
-      </c>
-      <c r="C98" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="D98" t="s">
-        <v>97</v>
-      </c>
-      <c r="E98" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A99" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B99" t="s">
-        <v>142</v>
-      </c>
-      <c r="C99" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="E99" t="s">
-        <v>156</v>
+        <v>138</v>
+      </c>
+      <c r="C98" t="s">
+        <v>91</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A100" t="s">
-        <v>90</v>
-      </c>
-      <c r="B100" t="s">
-        <v>142</v>
-      </c>
-      <c r="C100" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="D100" t="s">
-        <v>11</v>
-      </c>
-      <c r="E100" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A101" t="s">
-        <v>90</v>
-      </c>
-      <c r="B101" t="s">
-        <v>142</v>
-      </c>
-      <c r="C101" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="D101" t="s">
-        <v>97</v>
-      </c>
-      <c r="E101" t="s">
-        <v>158</v>
-      </c>
+      <c r="A100" s="2"/>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C102" s="3"/>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C103" s="3"/>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C104" s="3"/>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C105" s="3"/>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C106" s="3"/>
+      <c r="A102" s="2"/>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A107" s="2"/>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A112" s="2"/>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A114" s="2"/>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="C118" s="3"/>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A119" s="2"/>
+      <c r="C119" s="4"/>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A122" s="2"/>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A126" s="2"/>
+      <c r="C126" s="3"/>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="C127" s="3"/>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A128" s="2"/>
+      <c r="C128" s="3"/>
+    </row>
+    <row r="129" spans="3:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="C129" s="3"/>
+    </row>
+    <row r="130" spans="3:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="C130" s="3"/>
+    </row>
+    <row r="131" spans="3:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="C131" s="3"/>
+    </row>
+    <row r="132" spans="3:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="C132" s="3"/>
+    </row>
+    <row r="133" spans="3:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="C133" s="3"/>
+    </row>
+    <row r="134" spans="3:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="C134" s="3"/>
+    </row>
+    <row r="135" spans="3:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="C135" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="A1:XFD1048576">
+  <conditionalFormatting sqref="A1:XFD50 A51:B52 D51:XFD55 C52 A53:C55 A56:XFD1048576">
     <cfRule type="containsBlanks" dxfId="0" priority="1">
       <formula>LEN(TRIM(A1))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/hints.xlsx
+++ b/hints.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Xenia160100\Documents\GitHub\aozakana\GOD-KNOWS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFCD2EEE-B808-4B5F-9A8E-538C48C33850}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77298143-BCD7-435D-A153-A0C3B3DE3F0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" xr2:uid="{E69F9E97-3D7F-4EEF-852A-49F659DA4124}"/>
   </bookViews>
@@ -631,61 +631,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>メダルの色の「きん」「ぎん」「どう」が埋まったときに答えがドンになるには、もともと見えている範囲を考慮すると、画像のようになります。&lt;img src="img/1_5.png" class="w-full"&gt;&lt;br&gt;では、ここに埋めるべき漢字の音読みとは何でしょうか？パーツの個数が1、2、3個あること、「モク」という読みのものがあるという点から候補を絞りましょう。</t>
-    <rPh sb="4" eb="5">
-      <t>イロ</t>
-    </rPh>
-    <rPh sb="19" eb="20">
-      <t>ウ</t>
-    </rPh>
-    <rPh sb="26" eb="27">
-      <t>コタ</t>
-    </rPh>
-    <rPh sb="41" eb="42">
-      <t>ミ</t>
-    </rPh>
-    <rPh sb="46" eb="48">
-      <t>ハンイ</t>
-    </rPh>
-    <rPh sb="49" eb="51">
-      <t>コウリョ</t>
-    </rPh>
-    <rPh sb="55" eb="57">
-      <t>ガゾウ</t>
-    </rPh>
-    <rPh sb="114" eb="115">
-      <t>ウ</t>
-    </rPh>
-    <rPh sb="119" eb="121">
-      <t>カンジ</t>
-    </rPh>
-    <rPh sb="122" eb="124">
-      <t>オンヨ</t>
-    </rPh>
-    <rPh sb="127" eb="128">
-      <t>ナン</t>
-    </rPh>
-    <rPh sb="138" eb="140">
-      <t>コスウ</t>
-    </rPh>
-    <rPh sb="146" eb="147">
-      <t>コ</t>
-    </rPh>
-    <rPh sb="159" eb="160">
-      <t>ヨ</t>
-    </rPh>
-    <rPh sb="170" eb="171">
-      <t>テン</t>
-    </rPh>
-    <rPh sb="173" eb="175">
-      <t>コウホ</t>
-    </rPh>
-    <rPh sb="176" eb="177">
-      <t>シボ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>全体構造として、A、B、Cはそれぞれの問題を解くのに他の問題の答えが必要になります。解きやすい順番は提示しておきますが、ヒントは任意の順番で見ることができます。</t>
     <rPh sb="0" eb="2">
       <t>ゼンタイ</t>
@@ -812,10 +757,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>この二重枠はステップ1の5問目にありました。ステップ1の5問目の答えは「ドン」でした。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ステップ1の5問目と同様に、Aの文字数も2文字であると推測できます。よって、消去法でORACLEはCに適用されると分かります。</t>
     <rPh sb="7" eb="9">
       <t>モンメ</t>
@@ -826,22 +767,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ORACLEはCに適用されるため、答えは理論であると分かります。</t>
-    <rPh sb="9" eb="11">
-      <t>テキヨウ</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>コタ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>リロン</t>
-    </rPh>
-    <rPh sb="26" eb="27">
-      <t>ワ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>木、林、森の音読みのモク、シン、リンを埋め、答えは「シン」になります。</t>
     <rPh sb="0" eb="1">
       <t>キ</t>
@@ -924,122 +849,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>立方体の展開図は下のようになります。&lt;br&gt;　　り&lt;br&gt;　しろあん&lt;br&gt;　　ん&lt;br&gt;また、Aの答えの最初と最後の文字「し」「ん」を除いてSからGまでたどる方法は1通りしかありません。移動するルートが分かれば、配置方法・文字の拾い方も判明します。移動ルートを特定しましょう。&lt;br&gt;次のヒントでは移動ルートを提示します。</t>
-    <rPh sb="0" eb="3">
-      <t>リッポウタイ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>テンカイ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ズ</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>シタ</t>
-    </rPh>
-    <rPh sb="50" eb="51">
-      <t>コタ</t>
-    </rPh>
-    <rPh sb="53" eb="55">
-      <t>サイショ</t>
-    </rPh>
-    <rPh sb="56" eb="58">
-      <t>サイゴ</t>
-    </rPh>
-    <rPh sb="59" eb="61">
-      <t>モジ</t>
-    </rPh>
-    <rPh sb="68" eb="69">
-      <t>ノゾ</t>
-    </rPh>
-    <rPh sb="80" eb="82">
-      <t>ホウホウ</t>
-    </rPh>
-    <rPh sb="84" eb="85">
-      <t>トオ</t>
-    </rPh>
-    <rPh sb="94" eb="96">
-      <t>イドウ</t>
-    </rPh>
-    <rPh sb="102" eb="103">
-      <t>ワ</t>
-    </rPh>
-    <rPh sb="107" eb="109">
-      <t>ハイチ</t>
-    </rPh>
-    <rPh sb="109" eb="111">
-      <t>ホウホウ</t>
-    </rPh>
-    <rPh sb="112" eb="114">
-      <t>モジ</t>
-    </rPh>
-    <rPh sb="115" eb="116">
-      <t>ヒロ</t>
-    </rPh>
-    <rPh sb="117" eb="118">
-      <t>カタ</t>
-    </rPh>
-    <rPh sb="125" eb="127">
-      <t>イドウ</t>
-    </rPh>
-    <rPh sb="131" eb="133">
-      <t>トクテイ</t>
-    </rPh>
-    <rPh sb="143" eb="144">
-      <t>ツギ</t>
-    </rPh>
-    <rPh sb="150" eb="152">
-      <t>イドウ</t>
-    </rPh>
-    <rPh sb="156" eb="158">
-      <t>テイジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>移動ルートは以下のようになります。このルートで1回転がすと水色の面が上になるように配置し、ア行の面が上になるマスの文字を読みましょう。&lt;img src="img/4_matome_ans.png" class="w-full"&gt;</t>
-    <rPh sb="0" eb="2">
-      <t>イドウ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>イカ</t>
-    </rPh>
-    <rPh sb="24" eb="25">
-      <t>カイ</t>
-    </rPh>
-    <rPh sb="25" eb="26">
-      <t>コロ</t>
-    </rPh>
-    <rPh sb="29" eb="31">
-      <t>ミズイロ</t>
-    </rPh>
-    <rPh sb="32" eb="33">
-      <t>メン</t>
-    </rPh>
-    <rPh sb="34" eb="35">
-      <t>ウエ</t>
-    </rPh>
-    <rPh sb="41" eb="43">
-      <t>ハイチ</t>
-    </rPh>
-    <rPh sb="46" eb="47">
-      <t>ギョウ</t>
-    </rPh>
-    <rPh sb="48" eb="49">
-      <t>メン</t>
-    </rPh>
-    <rPh sb="50" eb="51">
-      <t>ウエ</t>
-    </rPh>
-    <rPh sb="57" eb="59">
-      <t>モジ</t>
-    </rPh>
-    <rPh sb="60" eb="61">
-      <t>ヨ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>答えは「ぜったい（絶対）」です。</t>
     <rPh sb="0" eb="1">
       <t>コタ</t>
@@ -1109,68 +918,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>グループIのしりとりは「ちょうぼ、ぼりびあ、あかねこ、こうし」、グループIIは「ちんか、かろりー、りょう、うかんむり」です。これらにしりとりが成立するように1単語追加することを考えましょう。次のヒントで示されるある事実を用いれば、追加することができる位置をそれぞれ2箇所まで限定することができます。</t>
-    <rPh sb="71" eb="73">
-      <t>セイリツ</t>
-    </rPh>
-    <rPh sb="79" eb="81">
-      <t>タンゴ</t>
-    </rPh>
-    <rPh sb="81" eb="83">
-      <t>ツイカ</t>
-    </rPh>
-    <rPh sb="88" eb="89">
-      <t>カンガ</t>
-    </rPh>
-    <rPh sb="95" eb="96">
-      <t>ツギ</t>
-    </rPh>
-    <rPh sb="101" eb="102">
-      <t>シメ</t>
-    </rPh>
-    <rPh sb="107" eb="109">
-      <t>ジジツ</t>
-    </rPh>
-    <rPh sb="110" eb="111">
-      <t>モチ</t>
-    </rPh>
-    <rPh sb="115" eb="117">
-      <t>ツイカ</t>
-    </rPh>
-    <rPh sb="125" eb="127">
-      <t>イチ</t>
-    </rPh>
-    <rPh sb="133" eb="135">
-      <t>カショ</t>
-    </rPh>
-    <rPh sb="137" eb="139">
-      <t>ゲンテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>重要なのは、Cの問題にあるボードです。これを見ると、唯一の2文字であるAの答えの最後の文字を矢印の3文字目が通っています。これが意味するのは、AとCは最後の文字が同じであるということです。この事実を用いて、A、Cの答えを追加できる位置を絞りましょう。</t>
-    <rPh sb="96" eb="98">
-      <t>ジジツ</t>
-    </rPh>
-    <rPh sb="99" eb="100">
-      <t>モチ</t>
-    </rPh>
-    <rPh sb="107" eb="108">
-      <t>コタ</t>
-    </rPh>
-    <rPh sb="110" eb="112">
-      <t>ツイカ</t>
-    </rPh>
-    <rPh sb="115" eb="117">
-      <t>イチ</t>
-    </rPh>
-    <rPh sb="118" eb="119">
-      <t>シボ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ヒント5</t>
   </si>
   <si>
@@ -1302,175 +1049,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>以下の考察により、A、Cの単語を追加する位置はグループI、IIともに先頭で、A、Cいずれも「ち」で終わる答えであることが分かります。これによりBの答えが確定します。&lt;br&gt;&lt;br&gt;「Cの答えがグループIIの最後尾につく」場合、Cの答えの1文字目は「り」です。また、このときBの答えの2文字目は「ろ」になります。まとめの謎の展開図からB、Cの答えの2文字目は一致するため、この場合Cの答えは「りろ？」となります。このような単語は「りろん」しかないので、どうやら1回目と同じ答えに帰着してしまいそうです。&lt;br&gt;一方、「Aの答えがグループIの最後尾につく」場合、Cの答えがグループIIの最後以外の場所に入ることを仮定すると、「しち」「しか」「しり」「しう」の4つだけです。これらのうちまとめの謎の盤面に2文字とも書かれているのは「しち」「しか」だけであり、また「しち」だとグループIがループしてしまうことから、この場合のAの答えは「しか」、Cの答えは「か？か」だと確定します。しかし、Cの問題のボードに注目するとCの答えが「か？か」になるためには埋める語群に「か」を含む4文字の単語が2つ以上なければならないはずですが、そうではなく矛盾します。よって、「Aの答えがグループIの最後尾につく」わけではないようです。</t>
-    <rPh sb="0" eb="2">
-      <t>イカ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>コウサツ</t>
-    </rPh>
-    <rPh sb="60" eb="61">
-      <t>ワ</t>
-    </rPh>
-    <rPh sb="73" eb="74">
-      <t>コタ</t>
-    </rPh>
-    <rPh sb="76" eb="78">
-      <t>カクテイ</t>
-    </rPh>
-    <rPh sb="93" eb="94">
-      <t>コタ</t>
-    </rPh>
-    <rPh sb="110" eb="112">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="115" eb="116">
-      <t>コタ</t>
-    </rPh>
-    <rPh sb="119" eb="121">
-      <t>モジ</t>
-    </rPh>
-    <rPh sb="121" eb="122">
-      <t>メ</t>
-    </rPh>
-    <rPh sb="138" eb="139">
-      <t>コタ</t>
-    </rPh>
-    <rPh sb="142" eb="144">
-      <t>モジ</t>
-    </rPh>
-    <rPh sb="144" eb="145">
-      <t>メ</t>
-    </rPh>
-    <rPh sb="159" eb="160">
-      <t>ナゾ</t>
-    </rPh>
-    <rPh sb="161" eb="163">
-      <t>テンカイ</t>
-    </rPh>
-    <rPh sb="163" eb="164">
-      <t>ズ</t>
-    </rPh>
-    <rPh sb="170" eb="171">
-      <t>コタ</t>
-    </rPh>
-    <rPh sb="174" eb="176">
-      <t>モジ</t>
-    </rPh>
-    <rPh sb="176" eb="177">
-      <t>メ</t>
-    </rPh>
-    <rPh sb="178" eb="180">
-      <t>イッチ</t>
-    </rPh>
-    <rPh sb="187" eb="189">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="191" eb="192">
-      <t>コタ</t>
-    </rPh>
-    <rPh sb="210" eb="212">
-      <t>タンゴ</t>
-    </rPh>
-    <rPh sb="230" eb="232">
-      <t>カイメ</t>
-    </rPh>
-    <rPh sb="233" eb="234">
-      <t>オナ</t>
-    </rPh>
-    <rPh sb="235" eb="236">
-      <t>コタ</t>
-    </rPh>
-    <rPh sb="238" eb="240">
-      <t>キチャク</t>
-    </rPh>
-    <rPh sb="254" eb="256">
-      <t>イッポウ</t>
-    </rPh>
-    <rPh sb="260" eb="261">
-      <t>コタ</t>
-    </rPh>
-    <rPh sb="269" eb="272">
-      <t>サイコウビ</t>
-    </rPh>
-    <rPh sb="276" eb="278">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="281" eb="282">
-      <t>コタ</t>
-    </rPh>
-    <rPh sb="291" eb="293">
-      <t>サイゴ</t>
-    </rPh>
-    <rPh sb="293" eb="295">
-      <t>イガイ</t>
-    </rPh>
-    <rPh sb="296" eb="298">
-      <t>バショ</t>
-    </rPh>
-    <rPh sb="299" eb="300">
-      <t>ハイ</t>
-    </rPh>
-    <rPh sb="304" eb="306">
-      <t>カテイ</t>
-    </rPh>
-    <rPh sb="344" eb="345">
-      <t>ナゾ</t>
-    </rPh>
-    <rPh sb="346" eb="348">
-      <t>バンメン</t>
-    </rPh>
-    <rPh sb="350" eb="352">
-      <t>モジ</t>
-    </rPh>
-    <rPh sb="354" eb="355">
-      <t>カ</t>
-    </rPh>
-    <rPh sb="405" eb="407">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="410" eb="411">
-      <t>コタ</t>
-    </rPh>
-    <rPh sb="420" eb="421">
-      <t>コタ</t>
-    </rPh>
-    <rPh sb="430" eb="432">
-      <t>カクテイ</t>
-    </rPh>
-    <rPh sb="442" eb="444">
-      <t>モンダイ</t>
-    </rPh>
-    <rPh sb="449" eb="451">
-      <t>チュウモク</t>
-    </rPh>
-    <rPh sb="456" eb="457">
-      <t>コタ</t>
-    </rPh>
-    <rPh sb="471" eb="472">
-      <t>ウ</t>
-    </rPh>
-    <rPh sb="474" eb="476">
-      <t>ゴグン</t>
-    </rPh>
-    <rPh sb="481" eb="482">
-      <t>フク</t>
-    </rPh>
-    <rPh sb="484" eb="486">
-      <t>モジ</t>
-    </rPh>
-    <rPh sb="487" eb="489">
-      <t>タンゴ</t>
-    </rPh>
-    <rPh sb="492" eb="494">
-      <t>イジョウ</t>
-    </rPh>
-    <rPh sb="514" eb="516">
-      <t>ムジュン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>答えは「こんぼう（棍棒）」です。</t>
     <rPh sb="0" eb="1">
       <t>コタ</t>
@@ -1663,79 +1241,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>立方体の展開図は下のようになります。&lt;br&gt;　　に&lt;br&gt;　こんぼう&lt;br&gt;　　ち&lt;br&gt;また、Aの答えの最初と最後の文字「も」「ち」を除いてSからGまでたどる方法は1通りしかありません。移動するルートが分かれば、配置方法・文字の拾い方も判明します。移動ルートを特定しましょう。&lt;br&gt;次のヒントでは移動ルートを提示します。</t>
-    <rPh sb="0" eb="3">
-      <t>リッポウタイ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>テンカイ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ズ</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>シタ</t>
-    </rPh>
-    <rPh sb="50" eb="51">
-      <t>コタ</t>
-    </rPh>
-    <rPh sb="53" eb="55">
-      <t>サイショ</t>
-    </rPh>
-    <rPh sb="56" eb="58">
-      <t>サイゴ</t>
-    </rPh>
-    <rPh sb="59" eb="61">
-      <t>モジ</t>
-    </rPh>
-    <rPh sb="68" eb="69">
-      <t>ノゾ</t>
-    </rPh>
-    <rPh sb="80" eb="82">
-      <t>ホウホウ</t>
-    </rPh>
-    <rPh sb="84" eb="85">
-      <t>トオ</t>
-    </rPh>
-    <rPh sb="94" eb="96">
-      <t>イドウ</t>
-    </rPh>
-    <rPh sb="102" eb="103">
-      <t>ワ</t>
-    </rPh>
-    <rPh sb="107" eb="109">
-      <t>ハイチ</t>
-    </rPh>
-    <rPh sb="109" eb="111">
-      <t>ホウホウ</t>
-    </rPh>
-    <rPh sb="112" eb="114">
-      <t>モジ</t>
-    </rPh>
-    <rPh sb="115" eb="116">
-      <t>ヒロ</t>
-    </rPh>
-    <rPh sb="117" eb="118">
-      <t>カタ</t>
-    </rPh>
-    <rPh sb="125" eb="127">
-      <t>イドウ</t>
-    </rPh>
-    <rPh sb="131" eb="133">
-      <t>トクテイ</t>
-    </rPh>
-    <rPh sb="143" eb="144">
-      <t>ツギ</t>
-    </rPh>
-    <rPh sb="150" eb="152">
-      <t>イドウ</t>
-    </rPh>
-    <rPh sb="156" eb="158">
-      <t>テイジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>答えは「もち（餅）」です。マスには「口（コウ）」「日（ニチ）」「目（モク）」が埋まります。</t>
     <rPh sb="0" eb="1">
       <t>コタ</t>
@@ -1936,6 +1441,465 @@
     </rPh>
     <rPh sb="63" eb="64">
       <t>コタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>この二重枠はステップ1の5問目にありました。ステップ1の5問目の答えは「ドン」です。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メダルの色の「きん」「ぎん」「どう」が埋まったときに答えがドンになるには、画像のようになっている必要があります。では、ここに埋めるべき漢字の音読みとは何でしょうか？パーツの個数が1、2、3個あること、「モク」という読みのものがあるという点から候補を絞りましょう。&lt;img src="img/1_5.png" class="w-full"&gt;</t>
+    <rPh sb="4" eb="5">
+      <t>イロ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>ガゾウ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ORACLEはCに適用されるため、答えは「りろん（理論）」であると分かります。</t>
+    <rPh sb="9" eb="11">
+      <t>テキヨウ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>リロン</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>ワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>立方体の展開図は下のようになります。&lt;br&gt;　　り&lt;br&gt;　しろあん&lt;br&gt;　　ん&lt;br&gt;また、Aの答えの最初と最後の文字「し」「ん」を除いてSからGまでたどる方法は1通りしかありません。移動するルートが分かれば、配置方法・文字の拾い方も判明します。移動ルートを特定しましょう。&lt;br&gt;次のヒントでは移動ルートを表示します。</t>
+    <rPh sb="0" eb="3">
+      <t>リッポウタイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>テンカイ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ズ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>シタ</t>
+    </rPh>
+    <rPh sb="50" eb="51">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="53" eb="55">
+      <t>サイショ</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>サイゴ</t>
+    </rPh>
+    <rPh sb="59" eb="61">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="68" eb="69">
+      <t>ノゾ</t>
+    </rPh>
+    <rPh sb="80" eb="82">
+      <t>ホウホウ</t>
+    </rPh>
+    <rPh sb="84" eb="85">
+      <t>トオ</t>
+    </rPh>
+    <rPh sb="94" eb="96">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="102" eb="103">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="107" eb="109">
+      <t>ハイチ</t>
+    </rPh>
+    <rPh sb="109" eb="111">
+      <t>ホウホウ</t>
+    </rPh>
+    <rPh sb="112" eb="114">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="115" eb="116">
+      <t>ヒロ</t>
+    </rPh>
+    <rPh sb="117" eb="118">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="125" eb="127">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="131" eb="133">
+      <t>トクテイ</t>
+    </rPh>
+    <rPh sb="143" eb="144">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="150" eb="152">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="156" eb="158">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>移動ルートは以下のようになります。このルートで1回転がすと水色の面が上になるように配置し、ア行の面が上になるマスの文字を読みましょう。&lt;br&gt;&lt;img src="img/4_matome_ans.png" class="w-full"&gt;</t>
+    <rPh sb="0" eb="2">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>コロ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ミズイロ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>メン</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>ハイチ</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>ギョウ</t>
+    </rPh>
+    <rPh sb="48" eb="49">
+      <t>メン</t>
+    </rPh>
+    <rPh sb="50" eb="51">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="57" eb="59">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="60" eb="61">
+      <t>ヨ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>グループIのしりとりは「ちょうぼ、ぼりびあ、あかねこ、こうし」、グループIIは「ちんか、かろりー、りょう、うかんむり」です。これらにしりとりが成立するように1単語追加することを考えましょう。次のヒントで示される「ある事実」を用いれば、追加することができる位置を限定することができます。</t>
+    <rPh sb="71" eb="73">
+      <t>セイリツ</t>
+    </rPh>
+    <rPh sb="79" eb="81">
+      <t>タンゴ</t>
+    </rPh>
+    <rPh sb="81" eb="83">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="88" eb="89">
+      <t>カンガ</t>
+    </rPh>
+    <rPh sb="95" eb="96">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="101" eb="102">
+      <t>シメ</t>
+    </rPh>
+    <rPh sb="108" eb="110">
+      <t>ジジツ</t>
+    </rPh>
+    <rPh sb="112" eb="113">
+      <t>モチ</t>
+    </rPh>
+    <rPh sb="117" eb="119">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="127" eb="129">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="130" eb="132">
+      <t>ゲンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>重要なのは、Cの問題にあるボードです。これを見ると、唯一2文字であるAの答えの最後の文字を矢印が通っています。これが意味するのは、AとCは最後の文字が同じであるということです。この事実を用いて、A、Cの答えを追加できる位置を絞りましょう。</t>
+    <rPh sb="90" eb="92">
+      <t>ジジツ</t>
+    </rPh>
+    <rPh sb="93" eb="94">
+      <t>モチ</t>
+    </rPh>
+    <rPh sb="101" eb="102">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="104" eb="106">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="109" eb="111">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="112" eb="113">
+      <t>シボ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>以下の考察により、A、Cの単語を追加する位置は「グループI、IIともに先頭」であることが分かります。これによりBの答えが確定します。&lt;br&gt;&lt;br&gt;「Cの答えがグループIIの最後尾につく」場合、Cの答えの1文字目は「り」です。また、このときBの答えの2文字目は「ろ」になります。まとめの謎の展開図からB、Cの答えの2文字目は一致するため、この場合Cの答えは「りろ？」となります。このような単語は「りろん」しかないので、どうやら1回目と同じ答えに帰着してしまいそうです。&lt;br&gt;&lt;br&gt;一方、「Aの答えがグループIの最後尾につく」場合、Cの答えがグループIIの最後以外の場所に入ることを仮定すると、「しち」「しか」「しり」「しう」の4つだけです。これらのうちまとめの謎の盤面に2文字とも書かれているのは「しち」「しか」だけであり、また「しち」だとグループIがループしてしまうことから、この場合のAの答えは「しか」、Cの答えは「か？か」だと確定します。しかし、Cの問題のボードに注目するとCの答えが「か？か」になるためには埋める語群に「か」を含む4文字の単語が2つ以上なければならないはずですが、実際はそうでないため矛盾します。よって、「Aの答えがグループIの最後尾につく」わけではないようです。</t>
+    <rPh sb="0" eb="2">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>コウサツ</t>
+    </rPh>
+    <rPh sb="44" eb="45">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="57" eb="58">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="60" eb="62">
+      <t>カクテイ</t>
+    </rPh>
+    <rPh sb="77" eb="78">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="94" eb="96">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="99" eb="100">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="103" eb="105">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="105" eb="106">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="122" eb="123">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="126" eb="128">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="128" eb="129">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="143" eb="144">
+      <t>ナゾ</t>
+    </rPh>
+    <rPh sb="145" eb="147">
+      <t>テンカイ</t>
+    </rPh>
+    <rPh sb="147" eb="148">
+      <t>ズ</t>
+    </rPh>
+    <rPh sb="154" eb="155">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="158" eb="160">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="160" eb="161">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="162" eb="164">
+      <t>イッチ</t>
+    </rPh>
+    <rPh sb="171" eb="173">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="175" eb="176">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="194" eb="196">
+      <t>タンゴ</t>
+    </rPh>
+    <rPh sb="214" eb="216">
+      <t>カイメ</t>
+    </rPh>
+    <rPh sb="217" eb="218">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="219" eb="220">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="222" eb="224">
+      <t>キチャク</t>
+    </rPh>
+    <rPh sb="242" eb="244">
+      <t>イッポウ</t>
+    </rPh>
+    <rPh sb="248" eb="249">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="257" eb="260">
+      <t>サイコウビ</t>
+    </rPh>
+    <rPh sb="264" eb="266">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="269" eb="270">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="279" eb="281">
+      <t>サイゴ</t>
+    </rPh>
+    <rPh sb="281" eb="283">
+      <t>イガイ</t>
+    </rPh>
+    <rPh sb="284" eb="286">
+      <t>バショ</t>
+    </rPh>
+    <rPh sb="287" eb="288">
+      <t>ハイ</t>
+    </rPh>
+    <rPh sb="292" eb="294">
+      <t>カテイ</t>
+    </rPh>
+    <rPh sb="332" eb="333">
+      <t>ナゾ</t>
+    </rPh>
+    <rPh sb="334" eb="336">
+      <t>バンメン</t>
+    </rPh>
+    <rPh sb="338" eb="340">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="342" eb="343">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="393" eb="395">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="398" eb="399">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="408" eb="409">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="418" eb="420">
+      <t>カクテイ</t>
+    </rPh>
+    <rPh sb="430" eb="432">
+      <t>モンダイ</t>
+    </rPh>
+    <rPh sb="437" eb="439">
+      <t>チュウモク</t>
+    </rPh>
+    <rPh sb="444" eb="445">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="459" eb="460">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="462" eb="464">
+      <t>ゴグン</t>
+    </rPh>
+    <rPh sb="469" eb="470">
+      <t>フク</t>
+    </rPh>
+    <rPh sb="472" eb="474">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="475" eb="477">
+      <t>タンゴ</t>
+    </rPh>
+    <rPh sb="480" eb="482">
+      <t>イジョウ</t>
+    </rPh>
+    <rPh sb="496" eb="498">
+      <t>ジッサイ</t>
+    </rPh>
+    <rPh sb="506" eb="508">
+      <t>ムジュン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>立方体の展開図は下のようになります。&lt;br&gt;　　に&lt;br&gt;　こんぼう&lt;br&gt;　　ち&lt;br&gt;また、Aの答えの最初と最後の文字「も」「ち」を除いてSからGまでたどる方法は1通りしかありません。移動するルートが分かれば、配置方法・文字の拾い方も判明します。移動ルートを特定しましょう。&lt;br&gt;次のヒントでは移動ルートを表示します。</t>
+    <rPh sb="0" eb="3">
+      <t>リッポウタイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>テンカイ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ズ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>シタ</t>
+    </rPh>
+    <rPh sb="50" eb="51">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="53" eb="55">
+      <t>サイショ</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>サイゴ</t>
+    </rPh>
+    <rPh sb="59" eb="61">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="68" eb="69">
+      <t>ノゾ</t>
+    </rPh>
+    <rPh sb="80" eb="82">
+      <t>ホウホウ</t>
+    </rPh>
+    <rPh sb="84" eb="85">
+      <t>トオ</t>
+    </rPh>
+    <rPh sb="94" eb="96">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="102" eb="103">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="107" eb="109">
+      <t>ハイチ</t>
+    </rPh>
+    <rPh sb="109" eb="111">
+      <t>ホウホウ</t>
+    </rPh>
+    <rPh sb="112" eb="114">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="115" eb="116">
+      <t>ヒロ</t>
+    </rPh>
+    <rPh sb="117" eb="118">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="125" eb="127">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="131" eb="133">
+      <t>トクテイ</t>
+    </rPh>
+    <rPh sb="143" eb="144">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="150" eb="152">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="156" eb="158">
+      <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3074,7 +3038,7 @@
         <v>86</v>
       </c>
       <c r="E50" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -3085,7 +3049,7 @@
         <v>95</v>
       </c>
       <c r="E51" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -3093,13 +3057,13 @@
         <v>86</v>
       </c>
       <c r="B52" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C52" t="s">
         <v>11</v>
       </c>
       <c r="E52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -3107,13 +3071,13 @@
         <v>86</v>
       </c>
       <c r="B53" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C53" t="s">
         <v>62</v>
       </c>
       <c r="E53" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -3121,13 +3085,13 @@
         <v>86</v>
       </c>
       <c r="B54" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C54" t="s">
         <v>63</v>
       </c>
       <c r="E54" t="s">
-        <v>105</v>
+        <v>137</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -3135,13 +3099,13 @@
         <v>86</v>
       </c>
       <c r="B55" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C55" t="s">
         <v>91</v>
       </c>
       <c r="E55" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -3169,7 +3133,7 @@
         <v>62</v>
       </c>
       <c r="E57" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -3183,7 +3147,7 @@
         <v>97</v>
       </c>
       <c r="E58" t="s">
-        <v>98</v>
+        <v>138</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -3197,7 +3161,7 @@
         <v>91</v>
       </c>
       <c r="E59" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -3211,7 +3175,7 @@
         <v>11</v>
       </c>
       <c r="E60" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -3225,7 +3189,7 @@
         <v>91</v>
       </c>
       <c r="E61" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -3236,7 +3200,7 @@
         <v>34</v>
       </c>
       <c r="E62" t="s">
-        <v>107</v>
+        <v>139</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -3250,7 +3214,7 @@
         <v>11</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="72" x14ac:dyDescent="0.55000000000000004">
@@ -3264,7 +3228,7 @@
         <v>62</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>112</v>
+        <v>140</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="54" x14ac:dyDescent="0.55000000000000004">
@@ -3278,7 +3242,7 @@
         <v>97</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>113</v>
+        <v>141</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -3292,12 +3256,12 @@
         <v>91</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="B67" t="s">
         <v>87</v>
@@ -3311,7 +3275,7 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="B68" t="s">
         <v>87</v>
@@ -3320,12 +3284,12 @@
         <v>61</v>
       </c>
       <c r="E68" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="B69" t="s">
         <v>87</v>
@@ -3339,7 +3303,7 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="B70" t="s">
         <v>87</v>
@@ -3348,24 +3312,24 @@
         <v>8</v>
       </c>
       <c r="E70" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="2" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="B71" t="s">
         <v>90</v>
       </c>
       <c r="C71" s="2"/>
       <c r="E71" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="2" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="B72" t="s">
         <v>90</v>
@@ -3374,49 +3338,49 @@
         <v>95</v>
       </c>
       <c r="E72" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="2" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="B73" t="s">
         <v>90</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="E73" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="2" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="B74" t="s">
         <v>90</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="D74" t="s">
         <v>11</v>
       </c>
       <c r="E74" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="2" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="B75" t="s">
         <v>90</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="D75" t="s">
         <v>61</v>
@@ -3427,13 +3391,13 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="2" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="B76" t="s">
         <v>90</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="D76" t="s">
         <v>63</v>
@@ -3444,13 +3408,13 @@
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="2" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="B77" t="s">
         <v>90</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="D77" t="s">
         <v>91</v>
@@ -3461,7 +3425,7 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="B78" t="s">
         <v>90</v>
@@ -3473,12 +3437,12 @@
         <v>11</v>
       </c>
       <c r="E78" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="B79" t="s">
         <v>90</v>
@@ -3490,12 +3454,12 @@
         <v>61</v>
       </c>
       <c r="E79" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="B80" t="s">
         <v>90</v>
@@ -3507,12 +3471,12 @@
         <v>63</v>
       </c>
       <c r="E80" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="B81" t="s">
         <v>90</v>
@@ -3524,12 +3488,12 @@
         <v>91</v>
       </c>
       <c r="E81" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="B82" t="s">
         <v>90</v>
@@ -3541,12 +3505,12 @@
         <v>11</v>
       </c>
       <c r="E82" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="B83" t="s">
         <v>90</v>
@@ -3558,12 +3522,12 @@
         <v>62</v>
       </c>
       <c r="E83" t="s">
-        <v>120</v>
+        <v>142</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="B84" t="s">
         <v>90</v>
@@ -3575,12 +3539,12 @@
         <v>97</v>
       </c>
       <c r="E84" t="s">
-        <v>121</v>
+        <v>143</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="B85" t="s">
         <v>90</v>
@@ -3592,12 +3556,12 @@
         <v>64</v>
       </c>
       <c r="E85" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="234" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="B86" t="s">
         <v>90</v>
@@ -3606,15 +3570,15 @@
         <v>33</v>
       </c>
       <c r="D86" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="B87" t="s">
         <v>90</v>
@@ -3626,12 +3590,12 @@
         <v>91</v>
       </c>
       <c r="E87" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="B88" t="s">
         <v>90</v>
@@ -3640,12 +3604,12 @@
         <v>34</v>
       </c>
       <c r="E88" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="B89" t="s">
         <v>90</v>
@@ -3657,12 +3621,12 @@
         <v>11</v>
       </c>
       <c r="E89" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="B90" t="s">
         <v>90</v>
@@ -3674,12 +3638,12 @@
         <v>61</v>
       </c>
       <c r="E90" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="B91" t="s">
         <v>90</v>
@@ -3691,12 +3655,12 @@
         <v>91</v>
       </c>
       <c r="E91" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="B92" t="s">
         <v>90</v>
@@ -3708,12 +3672,12 @@
         <v>11</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="B93" t="s">
         <v>90</v>
@@ -3725,12 +3689,12 @@
         <v>61</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="54" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="B94" t="s">
         <v>90</v>
@@ -3742,12 +3706,12 @@
         <v>63</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="B95" t="s">
         <v>90</v>
@@ -3759,46 +3723,46 @@
         <v>91</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="B96" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="B97" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="C97" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="B98" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="C98" t="s">
         <v>91</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.55000000000000004">
